--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -887,6 +887,37 @@
       <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Make AI quality a measurable, defended metric -- the exit gate for the whole AI layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 11 -- AI audit: safety (2026-10-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>From the end-to-end AI/RAG/agent audit: Dex and the Brain memory follow each screen's access rule; the unused agent endpoints are removed; WhatsApp accepts only live members, turns an approved instruction into a Desk draft, files nothing on its own unless the company opts in, and files a bill once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>An SME owner must be able to trust that the AI never shows a member what their own screens would not, and never creates work or books money that no person saw.</t>
         </is>
       </c>
     </row>
@@ -901,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -930,11 +961,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (38/38). Sprints 1-10 done, incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (48/48). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1299,6 +1329,43 @@
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Golden sets + CI regression gate, AI quality dashboard, model A/B benchmark harness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sprint 11</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>AI audit: safety + reliable Ask</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2057,7 +2124,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>DONE. services/ai/agent_tools.py: Tool registry {name,description,parameters(json-schema),fn,access=read|propose,permission}, register/tools_for(user) RBAC-filter (owner all; else by user_perms), to_schema (emergentintegrations function-tool format). services/ai/agent.py governed loop uses LlmChat native tool-calling (with_tools/send_message_with_tools/add_tool_result) wrapped in guarded_llm (budget/consent/quota/concurrency/timeout) + record_ai_call telemetry + INJECTION_GUARD. brain.agent prompt registered. LIVE-PROVEN.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. services/ai/agent_tools.py: Tool registry {name,description,parameters(json-schema),fn,access=read|propose,permission}, register/tools_for(user) RBAC-filter (owner all; else by user_perms), to_schema (emergentintegrations function-tool format). services/ai/agent.py governed loop uses LlmChat native tool-calling (with_tools/send_message_with_tools/add_tool_result) wrapped in guarded_llm (budget/consent/quota/concurrency/timeout) + record_ai_call telemetry + INJECTION_GUARD. brain.agent prompt registered. LIVE-PROVEN.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -2117,7 +2184,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>DONE. Per-conversation memory: run_agent takes conversation_id; _load_history feeds up to 6 prior turns back into the opening message; _save_turn persists {question,answer,tools_used} to db.agent_conversations. AgentRequest gained conversation_id. LIVE: 3 turns stored + context carried across turns.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. Per-conversation memory: run_agent takes conversation_id; _load_history feeds up to 6 prior turns back into the opening message; _save_turn persists {question,answer,tools_used} to db.agent_conversations. AgentRequest gained conversation_id. LIVE: 3 turns stored + context carried across turns.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -4218,7 +4285,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>DONE. Bounded observe-&gt;act-&gt;replan loop in run_agent: send_message_with_tools -&gt; while tool_calls and steps&lt;AGENT_MAX_STEPS(env,6): execute each tool -&gt; add_tool_result -&gt; continue -&gt; synthesize. HARD step budget stops runaway (unit-tested: always-tool script caps at max_steps). Unknown/RBAC-denied tool -&gt; error fed back, never crashes.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. Bounded observe-&gt;act-&gt;replan loop in run_agent: send_message_with_tools -&gt; while tool_calls and steps&lt;AGENT_MAX_STEPS(env,6): execute each tool -&gt; add_tool_result -&gt; continue -&gt; synthesize. HARD step budget stops runaway (unit-tested: always-tool script caps at max_steps). Unknown/RBAC-denied tool -&gt; error fed back, never crashes.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4278,7 +4345,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>DONE. Read tools (RBAC-gated): search_brain (RAG search_chunks, perm brain), list_open_tasks, finance_summary (exact receivables/payables from ledger -- agent never invents numbers, perm finance), get_contact (+outstanding), list_workflows (perm workflows). LIVE: agent called list_open_tasks+finance_summary in one step, answered from real data.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. Read tools (RBAC-gated): search_brain (RAG search_chunks, perm brain), list_open_tasks, finance_summary (exact receivables/payables from ledger -- agent never invents numbers, perm finance), get_contact (+outstanding), list_workflows (perm workflows). LIVE: agent called list_open_tasks+finance_summary in one step, answered from real data.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4338,7 +4405,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>DONE. propose_task tool (access=propose, perm voice_capture): files a pending_approval decision + blocked task (proposed_by_agent) into the EXISTING approval flow -- human approves, agent NEVER auto-executes. LIVE-PROVEN: 'chase Kumar' -&gt; decision '[AI proposed] Chase Kumar Traders for Unpaid Invoice' status pending_approval. Matches DecisionOS propose-&gt;approve DNA.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. propose_task tool (access=propose, perm voice_capture): files a pending_approval decision + blocked task (proposed_by_agent) into the EXISTING approval flow -- human approves, agent NEVER auto-executes. LIVE-PROVEN: 'chase Kumar' -&gt; decision '[AI proposed] Chase Kumar Traders for Unpaid Invoice' status pending_approval. Matches DecisionOS propose-&gt;approve DNA.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4398,12 +4465,582 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>DONE. should_use_agent(question) heuristic gate: open signals (why/what should/recommend/analyze/...) -&gt; agent; structured (how much/how many/list/overdue/...) -&gt; deterministic /ask; long unclassified -&gt; agent. Endpoint POST /api/brain/agent/run returns recommended_surface so UX routes. Unit-tested both classes.</t>
+          <t>REMOVED 2026-10-05 (E3-14.3: no screen used the agent; its tools read past RBAC). DONE. should_use_agent(question) heuristic gate: open signals (why/what should/recommend/analyze/...) -&gt; agent; structured (how much/how many/list/overdue/...) -&gt; deterministic /ask; long unclassified -&gt; agent. Endpoint POST /api/brain/agent/run returns recommended_surface so UX routes. Unit-tested both classes.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>Epic 3 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>E3-14.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>routers/brain.py _retrieve; services/record_access.py</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ask reads only what the asker's screens show</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>/ask returned every decision, contact (with phone numbers), leave record and memory note in the company to any member with Ask.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Each entity follows its own screen's rule from one shared module (services/record_access): decisions -&gt; visible_decisions_clause; contacts -&gt; crm_types; leaves -&gt; /leaves rule (own + ones you approve; all with Approve leave); memory -&gt; Brain access. Tasks already narrower than the task screen. Tests: test_ai_reads_what_the_screens_show.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>E3-14.2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>services/ai/brain_context.py query_context</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Brain memory rows follow the record they describe</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Approvals, workflow moves, meetings and resolved complaints were written to the Brain memory as "public", so Dex cited them to members who could not open the record.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. readable_context_rows checks every non-owner's rows at READ time against the record (decision visibility, workflow_scope, complaint_scope, meetings owner-only), so rows already stored are covered too; over-fetch keeps answers full. Regex fallback escaped. Verified live: a member sees 3 of 6 rows, the owner 6.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>E3-14.3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>routers/brain_router.py, services/ai/agent*.py, routers/dex.py</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Unused agent endpoints removed</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>/brain/agent, /brain/agent/run, /brain/agent/create-task and /dex/capture: no screen called them, and they read more than /ask allows (agent listed all 25 company tasks and any customer's dues to a Sales member, live).</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Routes, agent loop, tools, prompts (brain.agent_planner/agent_synth/agent), request models and model routes deleted; API baseline + routes.json updated. Live: all four return 404. /ask (numbers from code, words from AI) is the one Q&amp;A path.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>E3-14.4</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>services/whatsapp.py resolve_wa_tenant</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>A removed employee cannot WhatsApp in</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Removal soft-removes the membership but leaves the number on the user row, and routing never checked membership: a removed employee could still send bills and instructions into the company (and fall through to the WA_TENANT_ID catch-all).</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Only live members route (same rule as sign-in, split_by_membership); a known number with no live membership is dropped, never handed to the fallback. Note: WA_TENANT_ID still routes STRANGERS when set -- ops opt-in, unset by default.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>E3-14.5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>services/captures.py execute_capture; Captures.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>An approved WhatsApp instruction becomes a Desk draft</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Approving a WhatsApp capture ran a second, fresh AI extraction and approved it on the spot: its tasks, assignees and workflow moves (with override) were created without anyone seeing them.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. The decision now waits on the Desk with the reviewer's choices applied; the person it names approves the whole plan there (told, unless they are the reviewer). Toast: "Drafted on the Desk -- approve the plan there". Test: test_whatsapp_capture_becomes_a_desk_draft_and_the_desk_approves_it.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>E3-14.6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>services/captures.py + routers/captures.py approve</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Nothing files itself; approve files once</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>A WhatsApp bill under Rs 50,000 that the reading model rated itself &gt;=90% sure of was filed with no human; the limit ignored the company's own threshold. Two taps on Approve both executed (bill filed twice).</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Auto-file only when the company opts in (tenant.capture_auto_file, default off) and under its own high_value_threshold. Approve claims the draft atomically first (second tap: 400 Already processed). Tests: opt-in + threshold unit tests, two-taps e2e.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (AI audit: "fix the 1")</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>E3-14.7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>services/ai/brain_rbac.py; routers/brain.py _resolve_access</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ask access follows the data, not the words</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The Ask gate decided from WORDS in the question and hard-coded role names: Priya (team "Sales &amp; Order Management") was refused "what were our sales?" and her own order's status; a Finance-word in any question refused it.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. No word gate. One rule per kind of record, the same as its screen: tasks/decisions/leave/workload always (trimmed to scope), pipelines need Workflows, contacts need CRM, invoices/payments/expenses need Finance, notes need Brain, documents follow their own visibility. A refusal names the access it takes and lists what the person CAN ask. Export uses the same rule.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("hope the ask has the RBAC right ... make the ask more reliable")</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>E3-14.8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prompts/brain.py planner v1.1; routers/brain.py _refine_plan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Questions go to where the record lives</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The planner read "status of the Bluewave UK order" as invoices and "who is working on the Bluewave proforma invoice" as invoices.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Planner v1.1: orders/shipments/stages -&gt; workflows; a piece of work -&gt; tasks; money only when the answer is a figure; "mine" field; documents kind. Deterministic: who-is-working/is-it-done -&gt; tasks. When the planned records are closed and the question is not a money question, Ask answers from a named record the person CAN open (scored by keyword match) and says so in one sentence. Planner A/B: Sonnet 12/12 with v1.1; Haiku saved ~1s but misread 2 -- kept Sonnet.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("hope the ask has the RBAC right ... make the ask more reliable")</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>E3-14.9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>routers/brain.py _retrieve / _compute</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mine, names, open work, leave dates, follow-ups</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>"Show Priya Nair's overdue tasks" was empty (name matched against titles); "show my tasks" gave an owner everyone's; "what needs my attention today" told the owner she had nothing; "who is on leave this week" listed every leave ever; a follow-up could reuse another person's question.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. A teammate's name selects their work (within the asker's scope); my/for me = own records, but my team/company/attention and all/every do not; attention/focus questions = all open + overdue work; "pending" = every unfinished status; leave in a date window = overlapping; follow-up and export only on the asker's own question.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("hope the ask has the RBAC right ... make the ask more reliable")</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>E3-14.10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>routers/brain.py _answer; pages/AskAI.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Answers: Rs, no computed money, notes vs documents, readable</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Live answers said "$0 billed", called a saved note "the document in your workspace", totalled an order value for a salesperson, and said "none exist" for records the asker simply cannot see. In the Dex room the Restricted / Not-enough-information cards and KPI tiles were near-invisible (light glass card under light text).</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Answer rules: currency (Rs, Indian grouping); without Finance never compute/total money, quote only as written in a record they can open; notes/records are never called documents; non-owners hear "none that you can see". Room cards follow the dark room. Live matrix: 24+ questions x owner/Sales/Accounts/Tasks-only (~150 live answers) incl. Hindi + Tanglish, injection-style and gibberish; 9 deterministic tests (test_ask_access_follows_the_data) + rule tests.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("hope the ask has the RBAC right ... make the ask more reliable")</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -961,7 +961,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (48/48). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (51/51). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
         </is>
       </c>
     </row>
@@ -1340,17 +1340,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AI audit: safety + reliable Ask</t>
+          <t>AI audit: safety, reliable Ask, durable Brain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5044,6 +5044,182 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>E3-14.11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>routers/desk.py; prompts/coaching.py</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Desk briefing is a template, not an AI call</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GET /desk/summary called the LLM on every poll (every page, every 60 s) and no screen displayed the narrative: 41% of all AI calls and 71k tokens (~24% of a trial company's 300k monthly allowance) in the scratch company, spent on text nobody read.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. The `narrative` field is the existing deterministic template (Rs, no money for non-Finance). ai_desk_narrative, its cache and the desk.narrative prompt removed; test pins that the summary makes no AI call.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("push it and then do 2 and 3")</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>E3-14.12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>services/ai/brain_embed.py; brain_retrieval.py; brain_docs.py; tenant_wipe.py; files.py; AskAI.js; Brain*.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Brain</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Company Brain: durable index, relevance, live access, source links</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>The vector index silently ran in memory (no QDRANT_URL): wiped on every deploy and split between the 2 workers. No relevance cut-off (passages always injected, "I don't know" never fired). Deleted docs could stay citable; visibility edits re-ran OCR+embedding; embeddings skipped AI consent; tenant wipe left chunks + Brain files; PDFs were "concisely" summarised by vision; one 2400-char chunk per short doc; source chips unlabelled/dead.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Store chosen in one place: Qdrant (QDRANT_URL, one collection per model) else MongoDB brain_chunks (durable, shared, float32 + in-process cosine), memory only in tests. Index tag = store+model+chunker; startup backfill re-indexes only stale docs. Search: floor 0.30 + 0.15 margin (calibrated on text-embedding-3-small: relevant 0.40-0.73, unrelated 0.16-0.29), question + English keywords (Tanglish), LIVE doc decides existence + access (edit = no re-embed), skip embedding when nothing indexed. Indexing waits for AI consent; consent grant backfills. Section-aware chunks (one policy: 1 chunk -&gt; 4; relevant match 0.37 -&gt; 0.61-0.71). PDF text layer first (pypdf), DOCX tables. Whole passages to the answer. A strong public-document match answers a closed-area question. Tenant wipe erases chunks, vectors and Brain files. Source chips: typed + linked (decision/workflow/task/complaint/finance/document; meeting not clickable); Documents panel opens on the doc and shows why a file isn't searchable. Live: restart-durable, restrict/delete immediate, weather -&gt; "couldn't find".</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 ("push it and then do 2 and 3")</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>E3-14.13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Railway decision-os-mongo-db / production: qdrant service; backend QDRANT_URL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Qdrant on Railway, wired to the backend</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Production had no vector database: no Qdrant service and no QDRANT_URL, so the Brain index ran in memory per worker (before E3-14.12).</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>E3-14.12</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-05. Qdrant 1.19.2 (official image, Railway template "qdrant") in the production environment with a persistent volume at /qdrant/storage; PRIVATE only (no public domain), listening on [::]:6333, telemetry disabled. Backend QDRANT_URL = http://${{qdrant.RAILWAY_PRIVATE_DOMAIN}}:6333 (set without a redeploy; applies with the next deploy). Code: startup backfill is leader-only (scheduler_locks) so 2 workers do not embed twice; collection create is race-safe. AI keys verified present on backend: Anthropic, OpenAI, Gemini, Sarvam, Emergent. Note: WA_TENANT_ID is set in production (routes unknown WhatsApp senders into one company) -- owner decision.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("integrate in the railway directly")</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Backlog (next)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,7 +962,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (51/51). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (54/54). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1346,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1365,7 +1366,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5220,6 +5221,1122 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>E3-14.14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>routers/ledger.py; services/record_access.memory_scope</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Brain</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Finance amounts no longer leak through company notes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Every expense/asset/inventory/income was copied with its amount into db.memory, which any member with Brain access reads through Ask (and /memory, Brain search).</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06. The copy (_write_brain) is gone -- finance events are still recorded for the Brain as Finance-only history. Money notes already written (tags expense/asset/inventory/income) are visible only with Finance, on every read path.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("company brain separately … journal should be different from the brain")</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>E3-14.15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>routers/brain_notes.py; pages/CompanyBrain.js; brain_embed/brain_retrieval</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Brain</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Company Brain is its own place: Documents + Notes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Documents sat behind a toggle inside the Dex chat; notes had no screen (AI-written, shown only in the owner's Journal); any member could write notes via POST /memory; notes were keyword-only for Dex.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06. /company-brain (account menu + phone All Apps; Dex links to it): Documents and Notes tabs. Notes API: read with Brain access under who-can-see (public/team/owner &amp; managers) + Finance rule; add/edit/remove owner + Manage Team (founder's call; POST /memory follows). Notes show their source (added by / noted by Dex from a capture + decision link). Notes indexed beside documents ("note:&lt;id&gt;"), checked against the live note at search, cited as Note with a link. Live: a note added in the UI answered "what time should we phone Kumar Traders" by meaning; a member can read but not add.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("company brain separately … journal should be different from the brain")</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>E3-14.16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>routers/decisions.py /journal; pages/Journal.js; desk shortcut; AllAppsPanel</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Brain</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Journal is decision history for decision makers</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>The Journal was owner-only and mixed company notes into the decision log -- acting as half a knowledge store.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06. Decision Journal: decisions only (notes are the Brain's), gated require_perm("decisions_approve") (owner passes), each person sees the decisions they may open (visible_decisions_clause); menu/tile shown to decision makers. Live: owner 7 decisions, 0 notes; a member without approval rights refused.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("company brain separately … journal should be different from the brain")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Plan / notes</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>AB-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Remove WA_TENANT_ID from production</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Set on the Railway backend: WhatsApp from ANY unknown number lands in one company's capture queue.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Railway variable delete + verify an unknown sender is ignored (wa_events "ignored").</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>AB-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Settings: stop promising "use your own WhatsApp"</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>"AI and WhatsApp keys" card offers per-company WhatsApp Business keys; the code only ever uses the platform number (integrations/whatsapp.wa_token).</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Hide/relabel the WhatsApp rows until AB-04; keep AI keys honest too (tenant AI keys are also unused at runtime).</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>AB-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Approved templates: "approval waiting" + "task overdue" to the person</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Free-form messages only reach someone within 24h of their last message; proactive alerts need Meta-approved templates. The owner WhatsApp alert is a mock today.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Create + get approved 2 utility templates (EN + Tamil/Hindi); per-person opt-in; send from decision_flow notify + overdue sweep; fall back to in-app.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>AB-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Phase 2: connect the company's own WhatsApp number</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Customer/supplier messaging (payment reminders, dispatch updates, order intake) must come from the company, not DecisionOS.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Meta Tech Provider + Embedded Signup; per-tenant WABA/phone id/token; route inbound by receiving phone_number_id; per-tenant templates; check WhatsApp Business app coexistence availability in India.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>AB-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>AI consent (step 4)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>"AI off" must stop every AI path</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Gemini OCR/vision, speech-to-text (/transcribe, WhatsApp audio) and question embeddings run outside the consent gate.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Gate in integrations (gemini/stt/embeddings) by tenant consent; clear user message; tests per path.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AB-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>AI consent (step 4)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Lock down admin "reclassify purchases"</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/admin/reclassify-purchases runs AI over EVERY company's books with no tenant consent, budget or owner review, and rewrites expenses/assets.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Super-admin only, per-tenant, consent-checked, dry-run report the owner approves.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AB-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>AI consent (step 4)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Deleting a Brain document deletes its file</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Delete is soft (is_deleted) and the object stays in storage; tenant wipe now erases, single-document delete does not.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Delete object on delete (or after a grace period) -- DPDP erasure.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AB-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Calculated, not AI (step 5)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Expense category + purchase class by rules</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Fixed lists; keyword rules already exist (guess_expense_category / guess_asset_category). resync calls AI once per bill, sequentially.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Rules first, AI only when no rule matches; batch; show "suggested by rule".</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>AB-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Calculated, not AI (step 5)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Contact score + task priority score as formulas</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Both turn numbers we already compute into scores; formulas are repeatable and explainable.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Contact: outstanding, days late, complaints, deliveries. Task: due date, priority, blocked, revenue linkage.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AB-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Calculated, not AI (step 5)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Work coach + leave impact as rules/templates</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Prose over deterministic stats; leave impact is "least-loaded same team" + "extend if due in leave" (pick_least_loaded_member exists).</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AB-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Calculated, not AI (step 5)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Setup AI must not run on GET /auth/me</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>A page load can trigger up to 3 AI calls (lexicon / operating model / finance categories) and write them.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>One-time setup job + retry endpoint; /me never calls AI.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>AB-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Calculated, not AI (step 5)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Honest AI labels</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>"AI read your bill" shows when OCR failed; "AI suggests" may be the keyword guess; "Dex drafted a checklist" may be the canned 4 steps; Operating Score demo text shows to any company named "Kapoor".</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AB-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Ask latency 13-20 s</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Two Sonnet calls; the answer writer is the long pole.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Smaller context, stream the answer, cache identical questions.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AB-14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Finance brief caches "Not enough data" when AI fails</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>A consent/quota refusal is cached as if the books were empty until the figures change.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>AB-15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Chat attachments become permanent Brain documents</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Ask attach posts to /brain/documents (private); members without Manage Team get 403; every attachment is kept as a document.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>AB-16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Tamil/Tanglish stored as English translation</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sarvam runs in translate mode; fallbacks keep the original language.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Founder call: codemix (original words) recommended.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>AB-17</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Plans</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Trial AI allowance (300k tokens ~ 150 Ask questions/month)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Revisit now that the Desk briefing no longer uses ~24% of it.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AB-18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Backend logs go to stderr</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Railway marks every log line as "error", hiding real errors.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Log INFO to stdout.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>AB-19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Auto-file switch in Settings</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp auto-filing is off unless tenant.capture_auto_file is set -- no screen sets it.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Keep off for launch.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -962,10 +962,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (54/54). Sprints 1-11 done (S11 = 2026-10-05 AI audit safety fixes; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (55/55). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1346,12 +1347,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1366,7 +1367,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5389,6 +5390,63 @@
       <c r="L67" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 ("company brain separately … journal should be different from the brain")</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>E3-14.17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>services/calculated.py; services/finance_words.py; shared/money.py; routers/ledger,finance,tasks,operating_score,team,auth; services/ai/ai_setup.py; FinanceForms.jsx; MyWork.js; ContactProfile.js; WorkCoach.js; _operatingScoreDemo.js; i18n.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Calculated, not AI: category, purchase class, scores, coach, leave impact; no AI on /auth/me; honest labels</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Six Claude calls turned numbers or fixed lists the app already had into answers (expense category, expense/asset/stock, contact score, task priority, work review, leave cover): slow, different every time, unexplained, billed, and company data sent out. GET /auth/me could make up to 3 AI setup calls inline on a page load. Labels said "AI read your bill" when OCR failed, "AI suggests" for a keyword guess, and the Operating Score demo text showed to any company named "Kapoor".</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06. services/calculated: expense category = same vendor before -&gt; words used before -&gt; the company's own category names -&gt; keyword table -&gt; honest "choose a category" (says which decided it, shown under the suggestion); expense/asset/stock = vendor habit -&gt; asset words -&gt; goods/units (qty+unit read) -&gt; services -&gt; "unknown" (owner decides); whole-word matching ("cartons" is not a car, "current" is not rent). Contact score = paid share, outstanding, days since payment, volume, complaints; task priority = due date, priority, blocked, pipeline/revenue link (re-scored every call). Work coach = template over the person's stats; leave impact = least-loaded teammate in the same team, else move the date to the day after the leave, else watch. 6 AI functions + 6 prompts + routes + 10 golden cases retired (gate floors lowered with a note). /auth/me only claims a background setup fill (one worker, 10-min cooldown, fills only what is missing). Bill uploads return bill_read; toast says "the bill couldn't be read" when it wasn't; EN/HI/TA labels no longer say AI for calculated features; demo data gated on is_demo. tests/test_calculated_not_ai.py (24).</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("check the production logs and confirm qdrant indexing then solve the step 5")</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5884,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Rules first, AI only when no rule matches; batch; show "suggested by rule".</t>
+          <t>DONE 2026-10-06 (E3-14.17): rules only, no AI fallback -- vendor history, past words, company category names, keyword table; "choose" when nothing matches. Reason shown.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -5873,12 +5931,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Contact: outstanding, days late, complaints, deliveries. Task: due date, priority, blocked, revenue linkage.</t>
+          <t>DONE 2026-10-06 (E3-14.17): services/calculated.score_contact / score_tasks.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -5920,10 +5978,14 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06 (E3-14.17): services/calculated.work_coach / leave_impact (same team by task role, else the person's role; extend to the day after the leave).</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
@@ -5963,12 +6025,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>One-time setup job + retry endpoint; /me never calls AI.</t>
+          <t>DONE 2026-10-06 (E3-14.17): /me claims a background fill (atomic, 10-min cooldown); never calls AI inline.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -6010,10 +6072,14 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06 (E3-14.17): bill_read flag + "couldn't be read" toast; Smart priority / Suggested / Priority score / Relationship score / Work Coach without "AI"; demo gate = tenant.is_demo.</t>
+        </is>
+      </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 (AI audit follow-up)</t>

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -962,7 +962,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (55/55). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (56/56). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5447,6 +5447,68 @@
       <c r="L68" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 ("check the production logs and confirm qdrant indexing then solve the step 5")</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>E3-14.18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>routers/ledger.py; routers/admin.py; scripts/reclassify_purchases.py (deleted); services/calculated.py; pages/admin/AdminPortal.js + AdminSections.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Remove the "Fix Mis-booked Purchases" re-sync (admin button, owner endpoint, script)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>A one-time July 2026 cleanup for bills booked as expenses before upload-time classification. It rewrote every company's expenses/assets/stock and reset payment matching in one go, with no owner sign-off -- and could only overwrite what owners had chosen since.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>E3-14.17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06 (founder: "no need for the reclassify button"). Removed resync_finance + its helpers, POST /ledger/reclassify-purchases, POST/GET /admin/reclassify-purchases (+ the admin Maintenance tab, which held only that button), scripts/reclassify_purchases.py, and services/calculated.classify_purchase (no caller left). Upload still requires expense / asset / stock before a bill is filed; payment matching keeps balances current. API baseline regenerated (-3 routes).</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("no need for the reclassify button why we needed that ?" / "yes remove it")</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5852,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Super-admin only, per-tenant, consent-checked, dry-run report the owner approves.</t>
+          <t>DONE 2026-10-06 (E3-14.18): removed instead of locked down -- the admin button, its endpoints, the owner endpoint and the script are gone (founder: not needed).</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -962,11 +962,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (56/56). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (57/57). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1347,12 +1346,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1367,7 +1366,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed; Dex desktop pass (docked chat composer, readable answers, honest allowance message)</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5509,6 +5508,63 @@
       <c r="L69" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 ("no need for the reclassify button why we needed that ?" / "yes remove it")</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>E3-14.19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>pages/Brain.js; pages/brain/DexStage.jsx; pages/AskAI.js; lib/aiLimit.js; integrations/llm.py; services/ai/llm_limits.py</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Dex desktop pass: chat layout, readable answers, honest allowance message</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Checked in the browser at desktop width: the opener questions sat at the top of an empty page, far from the input; in a conversation the orb sat between thread and composer, the composer halved in width and scrolled off-screen under a long answer, and the page landed on the END of each answer. Tables printed stored values (sales_&amp;_order_management, todo, in_progress, 2026-09-22 wrapping at the hyphen); 20 sources were 20 chips; "DEX -&gt;" was glued to the first word. A company over its monthly AI allowance read "AI service error. Please try again." (the 402 detail was discarded) while the backend retried the same refusal on a second key and a fallback model.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-06. Desktop (md+): the composer docks to the bottom of the screen with a fade in the room colour, the thread fills the page above it, the orb steps out once a conversation exists, the column is full width, an answer scrolls its question to the top, the box grows as you type and has focus on arrival. Opener questions are cards under the composer (phones too). Answers: Dex avatar + name; table cells in words (department names, To do/Doing, High, 22 Sep, right-aligned numbers, no wrapped dates); 8 rows then "Show all"; 6 sources then "+N more"; refusals as a notice card. 402 allowance/budget says what ran out and the reset date (lib/aiLimit, reads lib/api detail_full). Backend: 402/451 not retried on other keys/models; refused coroutine closed. tests/test_dex_desktop_pass.py (9). Verified live on scratch (desktop 1024 + phone 375).</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-06 ("fix the UI of the desktop dex section ... understand the UX as well")</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6237,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Next version</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Smaller context, stream the answer, cache identical questions.</t>
+          <t>Next version (Yokesh 2026-10-07: "put the ASK speed in the backlogs ai. we will do that in next version"). Plan: stream the answer as it is written, cache identical questions per company, trim the context sent to the answer writer.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -962,10 +962,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (57/57). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (58/58). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1346,12 +1347,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1366,7 +1367,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed; Dex desktop pass (docked chat composer, readable answers, honest allowance message)</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed; Dex desktop pass (docked chat composer, readable answers, honest allowance message); AB-14/15/18 small fixes</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5565,6 +5566,63 @@
       <c r="L70" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 ("fix the UI of the desktop dex section ... understand the UX as well")</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>E3-14.20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>routers/ledger.py; pages/finance/FinanceAi.jsx; routers/brain.py; models/brain.py; hooks/useDexConversation.js; pages/Brain.js; pages/brain/DexStage.jsx; core/__init__.py</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AI backlog small fixes: honest finance brief, attachments read not filed, log levels</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AB-14: a brief that failed (allowance, AI off, timeout) was cached as "Not enough data yet" until the figures changed. AB-15: Ask filed every attachment into the Company Brain -- refused for members without Manage Team, permanent for everyone else; desktop Dex ignored a paperclip file when asking. AB-18: every log line went to stderr, which Railway marks "error".</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-07. AB-14: failure -&gt; {unavailable, headline: why}, not stored; panel shows a neutral note. AB-15: /files + AskRequest.file_ids; routers/brain._attached_files reads only the asker's own files (max 3, 6,000 chars each) into the answer as attached_files; a closed-records question still answers from the asker's own file without opening the records; cited "Attached". AB-18: INFO/WARNING -&gt; stdout, ERROR -&gt; stderr. Department names in Dex checked: the page already has the company's own list (earlier note was a refresh-timing mistake). tests/test_ai_backlog_small_fixes.py (8). Verified live on scratch: brief note over the allowance; a bill attached on desktop Dex answered from the file, 0 Brain documents created.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-07 ("first push then do this")</t>
         </is>
       </c>
     </row>
@@ -6284,10 +6342,14 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-07 (E3-14.20): a brief that could not be written is not cached; it says why (allowance used up / AI off / failed call) in a neutral note, and Refresh no longer says "refreshed" over it.</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
@@ -6327,10 +6389,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-07 (E3-14.20): Ask attachments go to /files and ride the question as file_ids; /ask reads only the asker's own files for that answer (cited "Attached"). Nothing is filed into the Company Brain. Desktop Dex now sends a paperclip file with the question too.</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-06 (AI audit follow-up)</t>
@@ -6460,12 +6526,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Log INFO to stdout.</t>
+          <t>DONE 2026-10-07 (E3-14.20): INFO/WARNING to stdout, ERROR+ to stderr (core._log_handlers).</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">

--- a/docs/DecisionOS_Epic3_AI_Foundation.xlsx
+++ b/docs/DecisionOS_Epic3_AI_Foundation.xlsx
@@ -962,7 +962,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (58/58). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
+          <t>Epic 3 AI Foundation -- ACTIVE SCOPE COMPLETE (59/59). Sprints 1-11 done (S11 = 2026-10-05/06 AI audit: safety fixes, durable Brain, and step 5 calculated-not-AI; the S4 agent was removed as unused), incl. S10 evals+benchmark: golden-set expansion + CI regression gate (E3-10.4) and the model-comparison benchmark harness (E3-10.6, evals/benchmark.py). Real-media items closed via Epic 10 S9: OCR quality (E3-06.1) + Tamil/Tanglish STT accuracy (E3-07.1). Remaining 12 out of active scope: 5 future-scoped (few-shot, feedback loop, per-tenant vocab, Voyage swap, embed-scope) + 7 Dex 'Ask' chips + per-role nav MOVED to Epic 6. Bug found+fixed while testing: BUG-16 (Gemini OCR model gemini-2.5-flash 404).</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed; Dex desktop pass (docked chat composer, readable answers, honest allowance message); AB-14/15/18 small fixes</t>
+          <t>Dex/Brain read only what the asker may; agent endpoints removed; WhatsApp: live members only, approval -&gt; Desk draft, no auto-filing by default, approve once; Ask redesigned: access follows the data (no word gate), questions reach the record they name, mine/names/open work/leave dates, Rs + no computed money, readable Dex room cards; Desk briefing no longer an AI call; Company Brain durable (Mongo/Qdrant), relevance cut-off, live access, section chunks, linked sources; Qdrant on Railway (private, persistent) wired via QDRANT_URL; Company Brain page (documents + notes in Qdrant, curated by owner + Manage Team); Journal = decision history for decision makers; finance-note leak closed; step 5: category, purchase class, contact/task scores, work coach and leave impact are calculated rules (no AI), /auth/me never calls AI, honest labels; the cross-company "reclassify purchases" re-sync removed; Dex desktop pass (docked chat composer, readable answers, honest allowance message); AB-14/15/18 small fixes; AB-05 AI off stops every AI path</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5623,6 +5623,63 @@
       <c r="L71" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-07 ("first push then do this")</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>E3-14.21</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>services/ai/llm_limits.py; routers/ledger.py; services/ingestion.py; services/vision.py; services/transcription.py; integrations/embeddings.py; services/whatsapp.py; pages/finance/FinanceForms.jsx</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>"AI off" stops every AI path (AB-05)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Only Claude calls (guarded_llm) checked the company's AI consent. With AI switched off, Gemini still read bills, documents and images on the company's own key; Sarvam/OpenAI/Whisper still transcribed voice and WhatsApp audio; OpenAI still embedded every Ask question -- company data still left for AI providers after the owner said no (DPDP).</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-07. require_ai_allowed(): the request's company (or one named), its consent checked before any provider call; no company (pre-signup) = nothing to check; a consent READ failure fails open like guarded_llm. Wired into ai_extract_ledger_file, ai_extract_document, ai_read_image_general, _transcribe_audio_full_local and embed_texts. Refusal is the existing 451 the app already explains. WhatsApp: 451 -&gt; "AI is switched off for your company...", 402 -&gt; allowance message (not "please try again"). Bill uploads return bill_note ("AI is switched off, so the bill wasn't read"). Out of scope by design: platform-admin key probes (no company data) and the signup interview voice (no company yet). tests/test_ai_off_everywhere.py (12). Live on scratch with consent revoked: bill saved unread with the note, Ask 451, backend log shows no provider attempt.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-07 ("only do the 1")</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5976,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Gate in integrations (gemini/stt/embeddings) by tenant consent; clear user message; tests per path.</t>
+          <t>DONE 2026-10-07 (E3-14.21): one gate (services/ai/llm_limits.require_ai_allowed) at every AI entry point outside guarded_llm -- Finance bill reading, document import, image/PDF reading, speech-to-text, embeddings. Refusal = the existing 451. WhatsApp replies "AI is switched off for your company" (and the allowance case) instead of "try again"; a bill upload says why it was not read.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
